--- a/archives/update_cards.xlsx
+++ b/archives/update_cards.xlsx
@@ -413,26 +413,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Tipo de issue</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Chave</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Resumo</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>DT. PREVISÃO ENTREGA</t>
         </is>
@@ -441,20 +446,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>MANTA-30807</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Manta</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30807</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>30439 PEDIDO AVULSO</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
@@ -463,20 +473,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>MANTA-30781</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Manta</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-30781</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>30911 PED AVULSO</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
